--- a/data/trans_orig/IP19_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19_R-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102008</t>
+          <t>101662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118318</t>
+          <t>118121</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>222544</t>
+          <t>222163</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46391</t>
+          <t>46319</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67899</t>
+          <t>66558</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44145</t>
+          <t>45001</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65029</t>
+          <t>66216</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97111</t>
+          <t>96696</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125566</t>
+          <t>126528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>185306</t>
+          <t>186647</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>206814</t>
+          <t>206886</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>188727</t>
+          <t>187540</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209611</t>
+          <t>208755</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>381395</t>
+          <t>380433</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>409850</t>
+          <t>410265</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59632</t>
+          <t>59789</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77047</t>
+          <t>77150</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60249</t>
+          <t>60226</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79376</t>
+          <t>79553</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124924</t>
+          <t>124318</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151052</t>
+          <t>151124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,17%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50501</t>
+          <t>50398</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67916</t>
+          <t>67759</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62139</t>
+          <t>61962</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81266</t>
+          <t>81289</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118011</t>
+          <t>117939</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144139</t>
+          <t>144745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,8%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84538</t>
+          <t>84062</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106452</t>
+          <t>106136</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76567</t>
+          <t>75847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98730</t>
+          <t>98258</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>166052</t>
+          <t>165622</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>197339</t>
+          <t>198734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,75%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86954</t>
+          <t>87270</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108868</t>
+          <t>109344</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107319</t>
+          <t>107791</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129482</t>
+          <t>130202</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>202116</t>
+          <t>200721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>233403</t>
+          <t>233833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,54%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>200664</t>
+          <t>200706</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>240991</t>
+          <t>241117</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>193080</t>
+          <t>193317</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>233369</t>
+          <t>231790</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>405580</t>
+          <t>408337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>464739</t>
+          <t>462948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>439339</t>
+          <t>439213</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>479666</t>
+          <t>479624</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>489331</t>
+          <t>490910</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>529620</t>
+          <t>529383</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>938291</t>
+          <t>940082</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>997450</t>
+          <t>994693</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141598</t>
+          <t>141643</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146138</t>
+          <t>146149</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140924</t>
+          <t>140267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284285</t>
+          <t>284064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45051</t>
+          <t>43926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66386</t>
+          <t>65311</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58138</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83087</t>
+          <t>82548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108118</t>
+          <t>108655</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139553</t>
+          <t>142314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>169864</t>
+          <t>170939</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>191199</t>
+          <t>192324</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>185160</t>
+          <t>185699</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>210109</t>
+          <t>209246</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>364944</t>
+          <t>362183</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>396379</t>
+          <t>395842</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72159</t>
+          <t>72274</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92328</t>
+          <t>92662</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>62510</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83415</t>
+          <t>83138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141747</t>
+          <t>142303</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170420</t>
+          <t>171177</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,24%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64715</t>
+          <t>64381</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84884</t>
+          <t>84769</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75156</t>
+          <t>75433</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96080</t>
+          <t>96061</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145194</t>
+          <t>144437</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>173867</t>
+          <t>173311</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70260</t>
+          <t>69665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92299</t>
+          <t>90851</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63323</t>
+          <t>62622</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83942</t>
+          <t>84706</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138311</t>
+          <t>138817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169225</t>
+          <t>170286</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79038</t>
+          <t>80486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101077</t>
+          <t>101672</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94720</t>
+          <t>93956</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115339</t>
+          <t>116040</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>180774</t>
+          <t>179713</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>211688</t>
+          <t>211182</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,34%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>199907</t>
+          <t>198122</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>239439</t>
+          <t>237449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>197577</t>
+          <t>197011</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>237848</t>
+          <t>237214</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>408588</t>
+          <t>409967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>463892</t>
+          <t>468490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>471952</t>
+          <t>473942</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>511484</t>
+          <t>513269</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>511552</t>
+          <t>512186</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>551823</t>
+          <t>552389</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>996899</t>
+          <t>992301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1052203</t>
+          <t>1050824</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>120969</t>
+          <t>120959</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>252599</t>
+          <t>252014</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36507</t>
+          <t>37164</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56280</t>
+          <t>56922</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46403</t>
+          <t>45951</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67846</t>
+          <t>67438</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87672</t>
+          <t>89486</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117727</t>
+          <t>117492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154237</t>
+          <t>153595</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174010</t>
+          <t>173353</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>190215</t>
+          <t>190623</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>211658</t>
+          <t>212110</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>350851</t>
+          <t>351086</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>380906</t>
+          <t>379092</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>80,9%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72184</t>
+          <t>71359</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94777</t>
+          <t>93944</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75067</t>
+          <t>75232</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98071</t>
+          <t>98244</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152189</t>
+          <t>153379</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184338</t>
+          <t>185826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,23%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94122</t>
+          <t>94955</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116715</t>
+          <t>117540</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90501</t>
+          <t>90328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113505</t>
+          <t>113340</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>193133</t>
+          <t>191645</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>225282</t>
+          <t>224092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73482</t>
+          <t>73129</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96034</t>
+          <t>95576</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56486</t>
+          <t>57298</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78519</t>
+          <t>78131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136277</t>
+          <t>134365</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169395</t>
+          <t>167761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77267</t>
+          <t>77725</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99819</t>
+          <t>100172</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95529</t>
+          <t>95917</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>117562</t>
+          <t>116750</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>177953</t>
+          <t>179587</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>211071</t>
+          <t>212983</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>61,32%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>193627</t>
+          <t>192453</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>234321</t>
+          <t>231535</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>191404</t>
+          <t>189228</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>233289</t>
+          <t>230300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>394224</t>
+          <t>396190</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>455617</t>
+          <t>453203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>470050</t>
+          <t>472836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>510744</t>
+          <t>511918</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>511555</t>
+          <t>514544</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>553440</t>
+          <t>555616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>993598</t>
+          <t>996012</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1054991</t>
+          <t>1053025</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50197</t>
+          <t>50194</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55863</t>
+          <t>55897</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60434</t>
+          <t>60379</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108800</t>
+          <t>108637</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115672</t>
+          <t>115743</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>29104</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46316</t>
+          <t>46433</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27141</t>
+          <t>26655</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45422</t>
+          <t>44566</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58901</t>
+          <t>59773</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84919</t>
+          <t>84680</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108727</t>
+          <t>108610</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126913</t>
+          <t>125939</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>134503</t>
+          <t>135359</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>152784</t>
+          <t>153270</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>250049</t>
+          <t>250288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>276067</t>
+          <t>275195</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42041</t>
+          <t>42267</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63339</t>
+          <t>62967</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75951</t>
+          <t>74940</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104311</t>
+          <t>103689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124830</t>
+          <t>125948</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160668</t>
+          <t>160362</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,4%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105715</t>
+          <t>106087</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127013</t>
+          <t>126787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>104835</t>
+          <t>105457</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133195</t>
+          <t>134206</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>217532</t>
+          <t>217838</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>253370</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,7%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66150</t>
+          <t>69280</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116743</t>
+          <t>116471</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87751</t>
+          <t>89402</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131286</t>
+          <t>133657</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>174081</t>
+          <t>171416</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>237254</t>
+          <t>237325</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157665</t>
+          <t>157937</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>208258</t>
+          <t>205128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168997</t>
+          <t>166626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>212532</t>
+          <t>210881</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>337437</t>
+          <t>337366</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>400610</t>
+          <t>403275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>162474</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>211914</t>
+          <t>212413</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>210840</t>
+          <t>210294</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>268717</t>
+          <t>266762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>384559</t>
+          <t>384336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>459488</t>
+          <t>461143</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>443261</t>
+          <t>442762</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>492701</t>
+          <t>495075</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>481654</t>
+          <t>483609</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>539531</t>
+          <t>540077</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>946058</t>
+          <t>944403</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1020987</t>
+          <t>1021210</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,102 +728,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3496</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>846</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4509</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4617</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3259</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5251</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1496</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5388</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>120730</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>117884</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>105325</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>101662</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>101554</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,2%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,65%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>120730</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>118121</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,31%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>342</t>
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>222163</t>
+          <t>222300</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>54166</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>43840</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>65498</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17,28%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>56662</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>46319</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>66558</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>46068</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>67671</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>22,38%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>54166</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>45001</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>66216</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>21,35%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96696</t>
+          <t>97126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126528</t>
+          <t>125566</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>199590</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>188258</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>209916</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>78,65%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>82,72%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>196543</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>186647</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>206886</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>185534</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>207137</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>77,62%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,71%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>199590</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>187540</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>208755</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>78,65%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>380433</t>
+          <t>381395</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>410265</t>
+          <t>409835</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>69826</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>60317</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>78913</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49,34%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>42,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,76%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>68652</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>59789</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>77150</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>60343</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>78422</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>53,82%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,88%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>60,49%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>69826</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>60226</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>79553</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>49,34%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124318</t>
+          <t>125888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151124</t>
+          <t>151525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>71689</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>62602</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>81198</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>44,24%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>57,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>58896</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>50398</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>67759</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>49126</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>67205</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>46,18%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>39,51%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>53,12%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>71689</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>61962</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>81289</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>50,66%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>117939</t>
+          <t>117538</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144745</t>
+          <t>143175</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,21%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>86682</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>75076</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>97551</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>42,07%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>36,44%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>47,34%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>95151</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>84062</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>106136</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>83800</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>106073</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>49,2%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>43,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>54,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>86682</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>75847</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>98258</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>42,07%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>165622</t>
+          <t>167985</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198734</t>
+          <t>198978</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,81%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>119367</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>108498</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>130973</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>57,93%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>52,66%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>63,56%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>98255</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>87270</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>109344</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>87333</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>109606</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>50,8%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>45,12%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>56,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>119367</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>107791</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>130202</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>57,93%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>200721</t>
+          <t>200477</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>233833</t>
+          <t>231470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>57,95%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>193406</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>193406</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>193406</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>211324</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>191783</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>230802</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>29,24%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26,54%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>221311</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>200706</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>241117</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>203349</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>241462</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>32,53%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>35,44%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>211324</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>193317</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>231790</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>29,24%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>408337</t>
+          <t>405780</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>462948</t>
+          <t>460145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>511376</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>491898</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>530917</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>70,76%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>73,46%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>692</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>459019</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>439213</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>479624</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>438868</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>476981</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>67,47%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>70,5%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>511376</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>490910</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>529383</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>70,76%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>940082</t>
+          <t>942885</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>994693</t>
+          <t>997250</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>680330</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>680330</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>680330</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3114</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1908</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5118</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5172</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3654</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -2783,74 +2783,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>143252</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>140807</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>143921</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>144853</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>141643</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>146149</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>141589</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>146143</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,7%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,48%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,58%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>143252</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>140267</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>143921</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>419</t>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284064</t>
+          <t>284245</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>290020</t>
+          <t>290025</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>143921</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>143921</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>143921</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>143921</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>143921</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>143921</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>70497</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>59450</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>83892</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>26,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>22,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>31,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>54333</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>43926</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>65311</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>44841</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>65172</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>23,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,59%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>27,64%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>70497</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>59001</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>82548</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>26,28%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108655</t>
+          <t>108787</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142314</t>
+          <t>141353</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>197750</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>184355</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>208797</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>73,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>68,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>77,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>181917</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>170939</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>192324</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>171078</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>191409</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>77,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>72,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>197750</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>185699</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>209246</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>73,72%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>362183</t>
+          <t>363144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>395842</t>
+          <t>395710</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268247</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268247</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268247</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268247</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268247</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268247</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>72882</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>62218</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>83076</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>45,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39,24%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>52,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>82348</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>72274</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>92662</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>71496</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>92503</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>52,44%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>59,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>72882</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>62510</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>83138</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>45,96%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142303</t>
+          <t>141430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171177</t>
+          <t>168452</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>85689</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>75495</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>96353</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>54,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>47,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>60,76%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>74695</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>64381</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>84769</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>64540</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>85547</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>47,56%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>41,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>53,98%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>85689</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>75433</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>96061</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>54,04%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144437</t>
+          <t>147162</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>173311</t>
+          <t>174184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>73356</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>62469</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>83672</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41,06%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>34,96%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>46,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>80458</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>69665</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>90851</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>69298</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>90564</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>46,96%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>40,66%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>53,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>73356</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>62622</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>84706</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>41,06%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138817</t>
+          <t>137684</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170286</t>
+          <t>169101</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,31%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>105306</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>94990</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>116193</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>58,94%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>53,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>65,04%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>90879</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>80486</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>101672</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>80773</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>102039</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>53,04%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>46,98%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>59,34%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>105306</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>93956</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>116040</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>58,94%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>179713</t>
+          <t>180898</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>211182</t>
+          <t>212315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,66%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>178662</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>178662</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>178662</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>178662</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>178662</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>178662</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>217403</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>197002</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>236228</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>29,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>31,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>314</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>219046</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>198122</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>237449</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>198759</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>239621</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>30,79%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>27,85%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33,38%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>217403</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>197011</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>237214</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>29,01%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>409967</t>
+          <t>407786</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>468490</t>
+          <t>463570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>531997</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>513172</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>552398</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>70,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>73,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>711</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>492345</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>473942</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>513269</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>471770</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>512632</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>69,21%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>66,62%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>72,15%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>531997</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>512186</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>552389</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>70,99%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>992301</t>
+          <t>997221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1050824</t>
+          <t>1053005</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,08%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>749400</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>749400</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>749400</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>749400</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>749400</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>749400</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,107 +4617,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>634</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3172</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3804</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>123530</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>120341</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,92%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>123530</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>120959</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>397</t>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>252014</t>
+          <t>252646</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,107 +4960,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56411</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>45895</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>69265</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>26,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>46030</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>37164</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>56922</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>37386</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>56211</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>21,87%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,65%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>27,04%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>56411</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>45951</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>67438</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>17,76%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>26,7%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>102441</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>87262</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>116938</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>21,86%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>17,81%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>102441</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>89486</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>117492</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>21,86%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -5073,107 +5073,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>201650</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>188796</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>212166</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>78,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>73,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>82,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>164487</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>153595</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>173353</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>154306</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>173131</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>78,13%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>72,96%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>201650</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>190623</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>212110</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>73,3%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>82,24%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>366137</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>351640</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>381316</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>78,14%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>82,19%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>366137</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>351086</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>379092</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>78,14%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,38%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>86432</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>74451</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>97183</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>45,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39,48%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>51,54%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>82919</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>71359</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>93944</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>72400</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>95314</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>43,9%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>86432</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>75232</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>98244</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>45,83%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>153379</t>
+          <t>154403</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>185826</t>
+          <t>185835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>102140</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>91389</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>114121</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>54,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>48,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>60,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>105980</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>94955</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>117540</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>93585</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>116499</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>56,1%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>50,27%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>62,22%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>102140</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>90328</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>113340</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>54,17%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>191645</t>
+          <t>191636</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>224092</t>
+          <t>223068</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,1%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>67237</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>56463</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>78148</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>32,44%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>44,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>84347</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>73129</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>95576</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>73748</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>96648</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>48,67%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>42,2%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>55,15%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>67237</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>57298</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>78131</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>38,63%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134365</t>
+          <t>135835</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167761</t>
+          <t>166814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,03%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>106811</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>95900</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>117585</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>61,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>55,1%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>67,56%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>88954</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>77725</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>100172</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>76653</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>99553</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>51,33%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>44,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>57,8%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>106811</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>95917</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>116750</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>61,37%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>179587</t>
+          <t>180534</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>212983</t>
+          <t>211513</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>60,89%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>210713</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>191031</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>232014</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>28,29%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25,65%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>213296</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>192453</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>231535</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>192744</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>232144</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>30,28%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>27,32%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>210713</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>189228</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>230300</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>28,29%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>396190</t>
+          <t>394078</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>453203</t>
+          <t>450867</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>534131</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>512830</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>553813</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>71,71%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,85%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>74,35%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>750</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>491075</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>472836</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>511918</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>472227</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>511627</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>69,72%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>67,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>72,68%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>774</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>534131</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>514544</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>555616</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>71,71%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>996012</t>
+          <t>998348</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1053025</t>
+          <t>1055137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,81%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4796</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2516</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>773</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6476</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>794</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>48471</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>45384</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49675</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,59%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,99%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>54154</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50194</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>55897</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>95,56%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58966</t>
+          <t>48929</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>45006</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60379</t>
+          <t>50623</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>113120</t>
+          <t>97400</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108637</t>
+          <t>93465</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115743</t>
+          <t>99817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50180</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50180</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50180</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>56670</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>56670</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>56670</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61018</t>
+          <t>51417</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61018</t>
+          <t>51417</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61018</t>
+          <t>51417</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>117687</t>
+          <t>101597</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>117687</t>
+          <t>101597</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>117687</t>
+          <t>101597</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>30853</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23470</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>39423</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15,13%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>36465</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>29104</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>46433</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>23,52%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35430</t>
+          <t>36170</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>27913</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44566</t>
+          <t>45064</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>71895</t>
+          <t>67023</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59773</t>
+          <t>56593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84680</t>
+          <t>79561</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>124242</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>115672</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>131625</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>80,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84,87%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>118578</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>108610</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>125939</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>76,48%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>144495</t>
+          <t>106207</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135359</t>
+          <t>97313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>153270</t>
+          <t>114464</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>263073</t>
+          <t>230448</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>250288</t>
+          <t>217910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>275195</t>
+          <t>240878</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>155095</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>155095</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>155095</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>155043</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>155043</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>155043</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>179925</t>
+          <t>142377</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>179925</t>
+          <t>142377</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>179925</t>
+          <t>142377</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>334968</t>
+          <t>297471</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>334968</t>
+          <t>297471</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>334968</t>
+          <t>297471</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>84900</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>72423</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>99483</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>43,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>36,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>50,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>51683</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>42267</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>62967</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>89994</t>
+          <t>53292</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74940</t>
+          <t>43000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103689</t>
+          <t>64526</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>141676</t>
+          <t>138192</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125948</t>
+          <t>120990</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160362</t>
+          <t>155436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>111997</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>97414</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>124474</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>56,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>49,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>63,22%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>117371</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>106087</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>126787</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>69,43%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>62,75%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>119152</t>
+          <t>117040</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>105457</t>
+          <t>105806</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134206</t>
+          <t>127332</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>236524</t>
+          <t>229038</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>217838</t>
+          <t>211794</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>246240</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>67,05%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>196897</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>196897</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>196897</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>169054</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>169054</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>169054</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>209146</t>
+          <t>170332</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>209146</t>
+          <t>170332</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>209146</t>
+          <t>170332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>378200</t>
+          <t>367230</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>378200</t>
+          <t>367230</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>378200</t>
+          <t>367230</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>103037</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>85165</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>122094</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>35,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>29,66%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>42,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>98549</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>69280</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>116471</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>35,91%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>42,44%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>107969</t>
+          <t>101474</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89402</t>
+          <t>87818</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133657</t>
+          <t>116203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>206518</t>
+          <t>204512</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>171416</t>
+          <t>181757</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>237325</t>
+          <t>229935</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>42,38%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>184124</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>165067</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>201996</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>64,12%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>57,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>70,34%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>175859</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>157937</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>205128</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>64,09%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>57,56%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74,75%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>192314</t>
+          <t>153922</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>166626</t>
+          <t>139193</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>210881</t>
+          <t>167578</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>368173</t>
+          <t>338046</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>337366</t>
+          <t>312623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>403275</t>
+          <t>360801</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>66,5%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>287161</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>287161</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>287161</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>274408</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>274408</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>274408</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>300283</t>
+          <t>255396</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>300283</t>
+          <t>255396</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>300283</t>
+          <t>255396</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>574691</t>
+          <t>542558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>574691</t>
+          <t>542558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>574691</t>
+          <t>542558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>220500</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>194283</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>245630</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>31,99%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>28,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>35,63%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>189213</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>160100</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>212413</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>28,88%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>235444</t>
+          <t>193425</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>210294</t>
+          <t>173608</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>266762</t>
+          <t>213379</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>424657</t>
+          <t>413924</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>384336</t>
+          <t>383023</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>461143</t>
+          <t>448051</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>468834</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>443704</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>495051</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>68,01%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>64,37%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>71,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>660</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>465962</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>442762</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>495075</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>71,12%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>67,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>75,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>514927</t>
+          <t>426098</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>483609</t>
+          <t>406144</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>540077</t>
+          <t>445915</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>980889</t>
+          <t>894932</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>944403</t>
+          <t>860805</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1021210</t>
+          <t>925833</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>70,74%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>928</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
